--- a/API Test Cases.xlsx
+++ b/API Test Cases.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/57ae40ef5b7945db/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="150" documentId="8_{96668C16-1C36-49A1-B878-BA735B73EA3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{904CB427-7EED-40C9-9768-0A50BBED6135}"/>
+  <xr:revisionPtr revIDLastSave="263" documentId="8_{96668C16-1C36-49A1-B878-BA735B73EA3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9B36C222-0D81-43B8-AD17-1276BF894E8E}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{5F7EEB71-1009-4B38-B3CA-1EE3082656CF}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="107">
   <si>
     <t>Test Case ID</t>
   </si>
@@ -343,6 +343,136 @@
 2.Create a new GET request.
 3.Enter endpoint-https://automationintesting.online/api/message/2
 4. Add Header: key-cookie,value-token=1e7dad9128ad33d
+5.Click Send.</t>
+  </si>
+  <si>
+    <t>Get Booking id with firstname</t>
+  </si>
+  <si>
+    <t>AUTH_007</t>
+  </si>
+  <si>
+    <t>Get Booking id with checkin=&amp;checkout= —date rangefilter</t>
+  </si>
+  <si>
+    <t>https://restful-booker.herokuapp.com/booking?checkin="2018-01-01"&amp;checkout="2019-01-01"</t>
+  </si>
+  <si>
+    <t>Date Range -check in-"2018-01-01" and checkout-"2019-01-01</t>
+  </si>
+  <si>
+    <t>1.Open API testing tool (e.g., Postman).
+2.Create a new GET request.
+3.Enter endpoint-https://restful-https://restful-booker.herokuapp.com/booking?checkin=&amp;checkout=
+4.Click Send.</t>
+  </si>
+  <si>
+    <t>Status code=200</t>
+  </si>
+  <si>
+    <t>Firstname- Sally</t>
+  </si>
+  <si>
+    <t>1.Open API testing tool (e.g., Postman).
+2.Create a new GET request.
+3.Enter endpoint-https://restful-booker.herokuapp.com/booking?firstname
+4.Click Send.</t>
+  </si>
+  <si>
+    <t> {
+    "firstname" : "Jim",
+    "lastname" : "Brown",
+    "totalprice" : 111,
+    "depositpaid" : true,
+    "bookingdates" : {
+        "checkin" : "2018-01-01",
+        "checkout" : "2019-01-01"
+    },
+    "additionalneeds" : "Breakfast"
+}</t>
+  </si>
+  <si>
+    <t>POST Booking</t>
+  </si>
+  <si>
+    <t>{
+    "firstname" : "Jim",
+    "lastname" : "Brown",
+    "totalprice" : 111,
+    "depositpaid" : true,
+    "bookingdates" : {
+        "checkin" : "2018-01-01",
+        "checkout" : "2019-01-01"
+    },
+    "additionalneeds" : "Breakfast"
+}</t>
+  </si>
+  <si>
+    <t>AUTH_10</t>
+  </si>
+  <si>
+    <t>Create Booking with missing firstname</t>
+  </si>
+  <si>
+    <t>{
+    "lastname" : "Brown",
+    "totalprice" : 111,
+    "depositpaid" : true,
+    "bookingdates" : {
+        "checkin" : "2018-01-01",
+        "checkout" : "2019-01-01"
+    },
+    "additionalneeds" : "Breakfast"
+}</t>
+  </si>
+  <si>
+    <t>Error</t>
+  </si>
+  <si>
+    <t>Internal server error</t>
+  </si>
+  <si>
+    <t>Create Booking with data/payload</t>
+  </si>
+  <si>
+    <t>AUTH_11</t>
+  </si>
+  <si>
+    <t>Create Booking with missing dates</t>
+  </si>
+  <si>
+    <t>{
+    "firstname" : "Jim",
+    "lastname" : "Brown",
+    "totalprice" : 111,
+    "depositpaid" : true,
+     "additionalneeds" : "Breakfast"
+}</t>
+  </si>
+  <si>
+    <t>AUTH_12</t>
+  </si>
+  <si>
+    <t>Update booking with all field with token</t>
+  </si>
+  <si>
+    <t>https://restful-booker.herokuapp.com/booking/:id</t>
+  </si>
+  <si>
+    <t>Token=1e7dad9128ad33d</t>
+  </si>
+  <si>
+    <t>1.Open API testing tool (e.g., Postman).
+2.Create a new PUT request.
+3.Enter endpoint-https://restful-https://restful-booker.herokuapp.com/booking
+4.Enter body mentioned in test data column
+5.Click Send.</t>
+  </si>
+  <si>
+    <t>1.Open API testing tool (e.g., Postman).
+2.Create a new POST request.
+3.Enter endpoint-https://restful-https://restful-booker.herokuapp.com/booking
+4.Enter body mentioned in test data column
 5.Click Send.</t>
   </si>
 </sst>
@@ -388,7 +518,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -411,9 +541,17 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -944,11 +1082,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5CBB8D95-9998-4353-884C-93C800DCC827}">
-  <dimension ref="A1:N16"/>
+  <dimension ref="A1:N18"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="10.265625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.53125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.33203125" customWidth="1"/>
     <col min="3" max="3" width="47.6640625" bestFit="1" customWidth="1"/>
     <col min="4" max="6" width="47.6640625" customWidth="1"/>
     <col min="7" max="7" width="26.1328125" bestFit="1" customWidth="1"/>
@@ -1048,6 +1186,9 @@
       <c r="A4" s="4" t="s">
         <v>35</v>
       </c>
+      <c r="B4" s="4" t="s">
+        <v>51</v>
+      </c>
       <c r="C4" s="4" t="s">
         <v>42</v>
       </c>
@@ -1080,6 +1221,9 @@
       <c r="A6" s="4" t="s">
         <v>36</v>
       </c>
+      <c r="B6" s="4" t="s">
+        <v>51</v>
+      </c>
       <c r="C6" s="4" t="s">
         <v>50</v>
       </c>
@@ -1098,46 +1242,249 @@
       <c r="I6" s="6" t="s">
         <v>46</v>
       </c>
+      <c r="M6" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="N6" s="4" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="D7" s="8" t="s">
+      <c r="A7" s="4"/>
+      <c r="C7" s="4"/>
+      <c r="D7" s="7"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="4"/>
+      <c r="H7" s="1"/>
+      <c r="I7" s="6"/>
+    </row>
+    <row r="8" spans="1:14" ht="71.25" x14ac:dyDescent="0.45">
+      <c r="A8" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="D8" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="H7" s="2"/>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="H8" s="2"/>
+      <c r="E8" t="s">
+        <v>43</v>
+      </c>
+      <c r="F8" t="s">
+        <v>87</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="I8" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="M8" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="N8" s="4" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.45">
       <c r="H9" s="2"/>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="H10" s="2"/>
+    <row r="10" spans="1:14" ht="99.75" x14ac:dyDescent="0.45">
+      <c r="A10" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="D10" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="E10" t="s">
+        <v>43</v>
+      </c>
+      <c r="F10" t="s">
+        <v>84</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="M10" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="N10" s="4" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.45">
       <c r="H11" s="2"/>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="H12" s="2"/>
+    <row r="12" spans="1:14" ht="181.15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A12" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="F12" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="I12" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="J12" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="M12" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="N12" s="4" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.45">
       <c r="H13" s="2"/>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="H14" s="2"/>
+    <row r="14" spans="1:14" ht="156.75" x14ac:dyDescent="0.45">
+      <c r="A14" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="F14" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="M14" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="N14" s="4" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.45">
       <c r="H15" s="2"/>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="H16" s="2"/>
+    <row r="16" spans="1:14" ht="99.75" x14ac:dyDescent="0.45">
+      <c r="A16" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="F16" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="I16" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="J16" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="M16" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="N16" s="4" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="H17" s="2"/>
+    </row>
+    <row r="18" spans="1:14" ht="156.75" x14ac:dyDescent="0.45">
+      <c r="A18" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="D18" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="E18" t="s">
+        <v>65</v>
+      </c>
+      <c r="F18" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="M18" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="N18" s="4" t="s">
+        <v>32</v>
+      </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="D2" r:id="rId1" xr:uid="{B13B64C4-0F58-4FB0-AE0B-AC86AE5E4800}"/>
     <hyperlink ref="D4" r:id="rId2" xr:uid="{B6E9AE8E-2C35-4D37-A3EB-33361A93F465}"/>
     <hyperlink ref="D6" r:id="rId3" xr:uid="{A2B46255-C0CA-413F-98CB-0A18BBA3D4DB}"/>
-    <hyperlink ref="D7" r:id="rId4" xr:uid="{DB0A84BA-2DE3-40EA-B4FB-536C9240AB81}"/>
+    <hyperlink ref="D8" r:id="rId4" xr:uid="{DB0A84BA-2DE3-40EA-B4FB-536C9240AB81}"/>
+    <hyperlink ref="D10" r:id="rId5" xr:uid="{C870198B-9018-4209-9FE7-355B8CA07FC0}"/>
+    <hyperlink ref="D18" r:id="rId6" xr:uid="{E563C3B5-E4F6-4627-B568-05C364AB2ABB}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1252,7 +1599,7 @@
       <c r="C4" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="D4" s="9" t="s">
+      <c r="D4" s="8" t="s">
         <v>60</v>
       </c>
       <c r="E4" s="4" t="s">
@@ -1284,7 +1631,7 @@
       <c r="C6" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="D6" s="9" t="s">
+      <c r="D6" s="8" t="s">
         <v>64</v>
       </c>
       <c r="E6" s="4" t="s">
@@ -1448,7 +1795,7 @@
       <c r="C4" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="D4" s="9" t="s">
+      <c r="D4" s="8" t="s">
         <v>75</v>
       </c>
       <c r="E4" s="4" t="s">
